--- a/product_selector_out/STM32U575-585.xlsx
+++ b/product_selector_out/STM32U575-585.xlsx
@@ -8702,9 +8702,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -9029,9 +9029,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -9356,9 +9356,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -9683,9 +9683,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -10010,9 +10010,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -10337,9 +10337,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -10664,9 +10664,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -10991,9 +10991,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -11318,9 +11318,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -11645,9 +11645,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -11972,9 +11972,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -12299,9 +12299,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -12626,9 +12626,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY24" s="6" t="inlineStr">
@@ -12953,9 +12953,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -13280,9 +13280,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -13607,9 +13607,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY27" s="6" t="inlineStr">
@@ -13934,9 +13934,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY28" s="6" t="inlineStr">
@@ -14261,9 +14261,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY29" s="6" t="inlineStr">
@@ -14588,9 +14588,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY30" s="6" t="inlineStr">
@@ -14915,9 +14915,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY31" s="6" t="inlineStr">
@@ -15242,9 +15242,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY32" s="6" t="inlineStr">
@@ -15338,7 +15338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15431,19 +15431,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32U585VI</t>
+          <t>STM32U575RG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15487,7 +15487,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -15497,19 +15497,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32U575RI</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15519,19 +15519,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32U575RI</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -15563,19 +15563,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -15592,12 +15592,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -15607,19 +15607,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -15629,14 +15629,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -15658,7 +15658,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -15680,7 +15680,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -15695,19 +15695,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -15717,19 +15717,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -15746,12 +15746,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -15761,19 +15761,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -15783,19 +15783,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -15805,19 +15805,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -15827,19 +15827,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -15856,12 +15856,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -15871,19 +15871,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -15893,14 +15893,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -15922,7 +15922,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -15944,7 +15944,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -15959,19 +15959,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15981,19 +15981,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -16010,12 +16010,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16025,19 +16025,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16047,19 +16047,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16069,19 +16069,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16091,19 +16091,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -16113,19 +16113,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -16135,19 +16135,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -16157,14 +16157,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16186,7 +16186,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -16208,7 +16208,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -16223,19 +16223,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -16245,19 +16245,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -16267,19 +16267,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -16289,19 +16289,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -16311,19 +16311,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -16333,19 +16333,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -16355,19 +16355,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -16377,19 +16377,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -16399,19 +16399,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -16421,14 +16421,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -16443,14 +16443,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -16465,14 +16465,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -16487,19 +16487,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16509,19 +16509,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16531,19 +16531,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16553,19 +16553,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16575,19 +16575,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16597,19 +16597,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16619,19 +16619,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16648,12 +16648,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16663,19 +16663,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16685,14 +16685,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U575QI</t>
+          <t>STM32U575OI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -16714,7 +16714,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U575QI</t>
+          <t>STM32U575OI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -16736,22 +16736,484 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>STM32U575OI</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32U575OI</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32U585OI</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32U585OI</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32U585OI</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32U585OI</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32U575QG</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32U575QG</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32U575QG</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32U575QG</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32U585QI</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32U585QI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32U585QI</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32U585QI</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32U585RI</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32U585RI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32U585RI</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32U585RI</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>STM32U575QI</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32U575QI</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32U575QI</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32U575QI</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32U575-585.xlsx
+++ b/product_selector_out/STM32U575-585.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM32"/>
+  <dimension ref="A1:BN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.91796875" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -7854,12 +7961,17 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -7880,16 +7992,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -7902,6 +8012,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -7921,7 +8032,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -7959,7 +8072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM32"/>
+  <dimension ref="A1:BN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8027,6 +8140,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8360,6 +8474,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -8455,6 +8574,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8777,7 +8897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9104,7 +9229,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9431,7 +9561,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9758,7 +9893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10085,7 +10225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10412,7 +10557,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10739,7 +10889,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11066,7 +11221,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11393,7 +11553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11720,7 +11885,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12047,7 +12217,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12374,7 +12549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12701,7 +12881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13028,7 +13213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13355,7 +13545,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13682,7 +13877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14009,7 +14209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14336,7 +14541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14663,7 +14873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14990,7 +15205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15317,7 +15537,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15325,8 +15550,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
